--- a/samples/mapping/invoice/invoice.xlsx
+++ b/samples/mapping/invoice/invoice.xlsx
@@ -890,7 +890,6 @@
         <x:v>12345.6</x:v>
       </x:c>
       <x:c r="F9" s="29">
-        <x:f>D9*E9</x:f>
         <x:v>30864</x:v>
       </x:c>
     </x:row>
@@ -929,7 +928,6 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="F11" s="29">
-        <x:f>D11*E11</x:f>
         <x:v>2000</x:v>
       </x:c>
     </x:row>
@@ -962,7 +960,6 @@
         <x:v>-500</x:v>
       </x:c>
       <x:c r="F13" s="29">
-        <x:f>D13*E13</x:f>
         <x:v>-500</x:v>
       </x:c>
     </x:row>
